--- a/astro-site/public/dl/taco-shop-checklist-templates/BONUS-01-taco-shop-pre-shift-meeting-template.xlsx
+++ b/astro-site/public/dl/taco-shop-checklist-templates/BONUS-01-taco-shop-pre-shift-meeting-template.xlsx
@@ -871,7 +871,7 @@
     <row r="36">
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Reservations:</t>
+          <t>Catering orders:</t>
         </is>
       </c>
       <c r="C36" s="8" t="n"/>
@@ -879,7 +879,7 @@
     <row r="37">
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Large parties:</t>
+          <t>Large orders:</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>
